--- a/Balibago_traci/batch_results/SP_DQN_Results.xlsx
+++ b/Balibago_traci/batch_results/SP_DQN_Results.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30 Runs  |  10 Normal  •  10 Slow  •  10 Jam  |  DQN trained model (test mode)</t>
+          <t>30 Runs  |  10 Normal  •  10 Slow  •  10 Jam  |  DQN trained model (integrated loop)</t>
         </is>
       </c>
     </row>
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>102.8687</v>
+        <v>105.3443</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>70.01600000000001</v>
+        <v>68.8081</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>2.4764</v>
+        <v>2.7016</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1435.6329</v>
+        <v>1440.069</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>3.2517</v>
+        <v>445.8994</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1.2361</v>
+        <v>41.9413</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>104.3565</v>
+        <v>104.7669</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>68.4483</v>
+        <v>67.3777</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2.5774</v>
+        <v>2.5616</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1428.233</v>
+        <v>1445.0747</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3.442</v>
+        <v>410.3145</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.1941</v>
+        <v>37.5457</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -689,22 +689,22 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>101.0031</v>
+        <v>103.9507</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>67.9164</v>
+        <v>69.1621</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2.2566</v>
+        <v>2.3886</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1425.0252</v>
+        <v>1486.8273</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2.984</v>
+        <v>377.3129</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1.0928</v>
+        <v>40.8035</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -714,22 +714,22 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>104.9952</v>
+        <v>106.376</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>67.8139</v>
+        <v>65.7094</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2.4266</v>
+        <v>2.4916</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1436.0337</v>
+        <v>1457.9818</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>3.3274</v>
+        <v>398.3287</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.9852</v>
+        <v>36.5394</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -739,22 +739,22 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>103.8423</v>
+        <v>106.7799</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>68.6341</v>
+        <v>68.00020000000001</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2.3541</v>
+        <v>2.6159</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1436.8857</v>
+        <v>1457.4337</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3.1266</v>
+        <v>412.2133</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1.1182</v>
+        <v>43.0601</v>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>103.29</v>
+        <v>103.1035</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>68.2068</v>
+        <v>66.6259</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2.4502</v>
+        <v>2.4624</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1409.4815</v>
+        <v>1418.7235</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>3.2586</v>
+        <v>404.462</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1.1568</v>
+        <v>38.0749</v>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
@@ -789,22 +789,22 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>100.9173</v>
+        <v>98.8991</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>68.4515</v>
+        <v>66.7158</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2.4042</v>
+        <v>2.3631</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1410.2484</v>
+        <v>1421.635</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>3.1755</v>
+        <v>342.341</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1.1701</v>
+        <v>32.9028</v>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
@@ -814,22 +814,22 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>102.5073</v>
+        <v>101.602</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>64.6026</v>
+        <v>64.81659999999999</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2.4587</v>
+        <v>2.3928</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1393.6094</v>
+        <v>1389.6458</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3.274</v>
+        <v>363.0636</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1.1542</v>
+        <v>36.5045</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>103.2973</v>
+        <v>101.2466</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>68.8013</v>
+        <v>68.1234</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>2.4349</v>
+        <v>2.4027</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1438.4885</v>
+        <v>1464.3746</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>3.1388</v>
+        <v>361.7986</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.3087</v>
+        <v>41.5416</v>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
@@ -864,22 +864,22 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>104.1621</v>
+        <v>102.5525</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>68.7333</v>
+        <v>68.26439999999999</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2.716</v>
+        <v>2.7023</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>1472.6687</v>
+        <v>1478.0691</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>3.6208</v>
+        <v>394.5977</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.2684</v>
+        <v>44.6378</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
@@ -896,22 +896,22 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>108.0047</v>
+        <v>106.0421</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>71.20269999999999</v>
+        <v>2103.2938</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>5.3583</v>
+        <v>1.8399</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2851.2385</v>
+        <v>996.3488</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>7.1597</v>
+        <v>275.1375</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>2.476</v>
+        <v>31.0615</v>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>103.1436</v>
+        <v>104.3698</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>70.1404</v>
+        <v>68.7454</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>4.7536</v>
+        <v>4.9382</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2841.3365</v>
+        <v>2849.8886</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>6.3526</v>
+        <v>780.9838</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>2.195</v>
+        <v>75.9723</v>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
@@ -946,22 +946,22 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>109.2098</v>
+        <v>105.4182</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>80.6009</v>
+        <v>91.8927</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>5</v>
+        <v>4.513</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2744.0969</v>
+        <v>2416.8788</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>6.8587</v>
+        <v>722.5886</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>2.0259</v>
+        <v>60.2441</v>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
@@ -971,22 +971,22 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>103.4219</v>
+        <v>103.8832</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>71.8878</v>
+        <v>82.708</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>4.9343</v>
+        <v>5.0789</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2772.865</v>
+        <v>2822.4138</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>6.5386</v>
+        <v>780.8149</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>2.3676</v>
+        <v>71.4503</v>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
@@ -996,22 +996,22 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>104.8768</v>
+        <v>107.2682</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>3108.5378</v>
+        <v>1265.1692</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>1.5349</v>
+        <v>1.9234</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>874.6321</v>
+        <v>1116.4213</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>2.0533</v>
+        <v>294.7076</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.7054</v>
+        <v>29.5893</v>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
@@ -1021,22 +1021,22 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>103.6269</v>
+        <v>103.5082</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>73.3173</v>
+        <v>607.99</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>5.059</v>
+        <v>2.7392</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2822.0577</v>
+        <v>1540.2901</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6.8995</v>
+        <v>405.5622</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>2.1142</v>
+        <v>39.8323</v>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
@@ -1046,22 +1046,22 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>99.0925</v>
+        <v>103.5159</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>985.3284</v>
+        <v>68.4729</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2.0349</v>
+        <v>4.902</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1193.076</v>
+        <v>2828.5099</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2.6895</v>
+        <v>683.1452</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.9875</v>
+        <v>75.91119999999999</v>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
@@ -1071,22 +1071,22 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>105.3531</v>
+        <v>107.1591</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>70.6854</v>
+        <v>1623.5448</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>5.2903</v>
+        <v>2.345</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2842.2187</v>
+        <v>1273.6853</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>6.94</v>
+        <v>352.9674</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>2.6508</v>
+        <v>37.7479</v>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>105.8011</v>
+        <v>104.526</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>85.09229999999999</v>
+        <v>297.9914</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>4.9132</v>
+        <v>3.0201</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2692.8305</v>
+        <v>1639.7688</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>6.5068</v>
+        <v>463.8658</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>2.3635</v>
+        <v>45.1841</v>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
@@ -1121,22 +1121,22 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>106.7685</v>
+        <v>107.5277</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>73.2963</v>
+        <v>71.5656</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>5.311</v>
+        <v>5.4942</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2831.48</v>
+        <v>2878.6543</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>6.9587</v>
+        <v>803.1528</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>2.6748</v>
+        <v>89.4528</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1153,22 +1153,22 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>133.8023</v>
+        <v>117.2083</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>87.586</v>
+        <v>72.51260000000001</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>7.8451</v>
+        <v>7.7228</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>4212.9296</v>
+        <v>4068.6521</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>10.6589</v>
+        <v>1088.4816</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>3.3429</v>
+        <v>102.2974</v>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>139.7413</v>
+        <v>112.5478</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>794.0101</v>
+        <v>2877.9782</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>3.1709</v>
+        <v>2.9703</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>1645.8208</v>
+        <v>1530.3488</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>4.1912</v>
+        <v>435.8938</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1.5384</v>
+        <v>42.6982</v>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
@@ -1203,22 +1203,22 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>150.6268</v>
+        <v>115.3431</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>1629.0672</v>
+        <v>3584.6697</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>3.0555</v>
+        <v>2.3729</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>1724.9848</v>
+        <v>1233.9131</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>3.9511</v>
+        <v>386.3343</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1.6224</v>
+        <v>36.8316</v>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
@@ -1228,22 +1228,22 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>130.1116</v>
+        <v>112.1292</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>88.4933</v>
+        <v>1232.9181</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>7.3548</v>
+        <v>3.1167</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>3912.6028</v>
+        <v>1713.0684</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>9.4818</v>
+        <v>434.1391</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>3.9515</v>
+        <v>46.2495</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
@@ -1253,22 +1253,22 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>135.7621</v>
+        <v>158.2225</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>83.44119999999999</v>
+        <v>111.1985</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>7.5299</v>
+        <v>7.283</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>4153.1205</v>
+        <v>4013.943</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>9.9407</v>
+        <v>1111.9647</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>3.6725</v>
+        <v>111.3497</v>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>152.9213</v>
+        <v>116.1375</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>1376.879</v>
+        <v>833.2174</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>2.7491</v>
+        <v>3.3721</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>1412.4324</v>
+        <v>1788.1263</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>3.6024</v>
+        <v>503.809</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.3837</v>
+        <v>46.2124</v>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>123.6839</v>
+        <v>130.1229</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>80.9709</v>
+        <v>160.8667</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>7.638</v>
+        <v>5.7</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>4018.6394</v>
+        <v>2934.9441</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>10.0204</v>
+        <v>826.0135</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3.8261</v>
+        <v>87.0761</v>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
@@ -1328,22 +1328,22 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>110.4618</v>
+        <v>140.5349</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>4767.5</v>
+        <v>453.6546</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1.9728</v>
+        <v>4.9439</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1073.6515</v>
+        <v>2682.8608</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>2.5483</v>
+        <v>759.062</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.0521</v>
+        <v>74.2697</v>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
@@ -1353,22 +1353,22 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>114.7362</v>
+        <v>122.0059</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>3241.6248</v>
+        <v>2103.8091</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>2.1865</v>
+        <v>2.8499</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>1134.1245</v>
+        <v>1495.5004</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>2.9007</v>
+        <v>412.872</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.0437</v>
+        <v>42.4453</v>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
@@ -1378,22 +1378,22 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>164.0784</v>
+        <v>136.618</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>93.398</v>
+        <v>86.6036</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>7.6239</v>
+        <v>7.6963</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>3925.0647</v>
+        <v>4004.3328</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>10.0252</v>
+        <v>1168.7874</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>3.7818</v>
+        <v>119.0527</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
